--- a/data/gravel/Gloria All Terrain 2025.xlsx
+++ b/data/gravel/Gloria All Terrain 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B847F24-283A-4D4C-9ED5-3FCD0D1FD45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2126A69-8D50-5B4E-94B0-438C5863F572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="2440" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5940" yWindow="1880" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -68,9 +68,6 @@
     <t>top_tube_effective_length</t>
   </si>
   <si>
-    <t>front_center</t>
-  </si>
-  <si>
     <t>head_tube_angle</t>
   </si>
   <si>
@@ -245,9 +242,6 @@
     <t>frame_weight</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -396,6 +390,15 @@
   </si>
   <si>
     <t>495 est</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>est 53</t>
   </si>
 </sst>
 </file>
@@ -775,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -783,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -807,12 +810,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -820,7 +823,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -828,27 +831,27 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" t="s">
         <v>95</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>96</v>
-      </c>
-      <c r="E8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9">
         <v>110</v>
@@ -865,10 +868,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10">
         <v>566</v>
@@ -883,7 +886,7 @@
         <v>638</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -891,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11">
         <v>410</v>
@@ -908,10 +911,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C12">
         <v>702</v>
@@ -931,7 +934,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13">
         <v>610</v>
@@ -948,10 +951,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>395</v>
@@ -968,10 +971,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C15">
         <v>435</v>
@@ -988,10 +991,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16">
         <v>75</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17">
         <v>68</v>
@@ -1028,10 +1031,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>1119</v>
@@ -1051,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C19">
         <f>C13/TAN(C16*PI()/180) + C11</f>
@@ -1070,12 +1073,12 @@
         <v>653.86055011486496</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20">
@@ -1091,7 +1094,7 @@
         <v>62</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H20" s="6">
         <v>62.581000000000003</v>
@@ -1102,38 +1105,89 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <v>506</v>
+      </c>
+      <c r="D21">
+        <v>506</v>
+      </c>
+      <c r="E21">
+        <v>506</v>
+      </c>
+      <c r="F21">
+        <v>506</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <v>51</v>
+      </c>
+      <c r="D22">
+        <v>51</v>
+      </c>
+      <c r="E22">
+        <v>51</v>
+      </c>
+      <c r="F22">
+        <v>51</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>11</v>
+      <c r="A23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1"/>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26">
         <v>2100</v>
@@ -1141,28 +1195,28 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30">
         <v>700</v>
@@ -1179,10 +1233,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31">
         <v>2.4</v>
@@ -1199,10 +1253,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32">
         <v>2.4</v>
@@ -1219,10 +1273,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33">
         <v>160</v>
@@ -1239,10 +1293,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34">
         <v>170</v>
@@ -1259,60 +1313,60 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
         <v>30</v>
-      </c>
-      <c r="B36" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" t="s">
         <v>32</v>
-      </c>
-      <c r="B40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43">
         <v>2.4</v>
@@ -1320,38 +1374,38 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45">
         <v>120</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49">
         <v>148</v>
@@ -1359,7 +1413,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50">
         <v>110</v>
@@ -1367,7 +1421,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B51">
         <v>44</v>
@@ -1375,57 +1429,57 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B59">
         <v>31.6</v>
@@ -1433,13 +1487,13 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B61">
         <v>38</v>
@@ -1447,17 +1501,17 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B64">
         <v>160</v>
@@ -1465,41 +1519,41 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1507,7 +1561,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -1515,7 +1569,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B72" s="1">
         <v>1</v>
@@ -1523,31 +1577,31 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B75" s="1"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B76" s="1"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B77">
         <v>1394.45</v>
@@ -1555,7 +1609,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B78">
         <v>3767.38</v>
@@ -1563,23 +1617,23 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
